--- a/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen otros</t>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 45,08</t>
+          <t>1,49; 43,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 17,49</t>
+          <t>3,86; 17,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,9; 26,72</t>
+          <t>5,17; 27,05</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,36</t>
+          <t>3,69; 7,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,83; 10,72</t>
+          <t>4,86; 10,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,41</t>
+          <t>4,84; 8,28</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 11,86</t>
+          <t>4,48; 12,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 14,48</t>
+          <t>5,38; 13,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,57</t>
+          <t>5,93; 11,61</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,97</t>
+          <t>4,8; 9,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,5</t>
+          <t>6,0; 10,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,09</t>
+          <t>5,88; 9,17</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7391</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13235</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>813; 23973</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2394; 11054</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6028; 31558</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>25113</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35227</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60340</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>16936; 33965</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>24901; 54193</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47038; 80441</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11300</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>16557</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27857</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6697; 18730</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9872; 25171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19750; 38654</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>43804</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>57628</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>101432</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>31833; 63484</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45454; 79980</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>83615; 130260</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 43,84</t>
+          <t>1,44; 44,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 17,83</t>
+          <t>4,39; 19,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 27,05</t>
+          <t>5,22; 26,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,4</t>
+          <t>3,7; 7,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 10,58</t>
+          <t>4,85; 10,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,28</t>
+          <t>4,78; 8,55</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 12,52</t>
+          <t>4,43; 11,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,73</t>
+          <t>5,37; 13,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,61</t>
+          <t>6,0; 11,32</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,57</t>
+          <t>4,89; 9,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,56</t>
+          <t>5,81; 10,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,17</t>
+          <t>5,87; 9,16</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>813; 23973</t>
+          <t>785; 24091</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2394; 11054</t>
+          <t>2721; 11793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6028; 31558</t>
+          <t>6095; 31280</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16936; 33965</t>
+          <t>16999; 34689</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24901; 54193</t>
+          <t>24833; 55766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47038; 80441</t>
+          <t>46411; 83065</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6697; 18730</t>
+          <t>6632; 17350</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9872; 25171</t>
+          <t>9853; 25158</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19750; 38654</t>
+          <t>19958; 37675</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31833; 63484</t>
+          <t>32406; 64999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45454; 79980</t>
+          <t>44031; 78467</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83615; 130260</t>
+          <t>83407; 130168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 44,06</t>
+          <t>3,9; 17,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 19,02</t>
+          <t>1,41; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 26,81</t>
+          <t>3,93; 12,79</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,56</t>
+          <t>4,12; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,88</t>
+          <t>4,36; 8,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,55</t>
+          <t>4,81; 7,46</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 11,6</t>
+          <t>6,14; 15,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 13,72</t>
+          <t>4,7; 12,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 11,32</t>
+          <t>6,22; 11,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,8</t>
+          <t>5,5; 9,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,36</t>
+          <t>4,89; 8,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,16</t>
+          <t>5,73; 8,11</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>7605</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>785; 24091</t>
+          <t>2210; 9666</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2721; 11793</t>
+          <t>661; 6147</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6095; 31280</t>
+          <t>4067; 13239</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>35227</t>
+          <t>26195</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60340</t>
+          <t>54070</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16999; 34689</t>
+          <t>19404; 37816</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24833; 55766</t>
+          <t>18802; 35861</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46411; 83065</t>
+          <t>43384; 67307</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27857</t>
+          <t>27657</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6632; 17350</t>
+          <t>10335; 25362</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9853; 25158</t>
+          <t>7049; 18641</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19958; 37675</t>
+          <t>19814; 38174</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>43804</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>57628</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101432</t>
+          <t>89332</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32406; 64999</t>
+          <t>38275; 63224</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44031; 78467</t>
+          <t>30664; 51401</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83407; 130168</t>
+          <t>75922; 107338</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1022_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 17,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 13,15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3,93; 12,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,12; 8,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,36; 8,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,81; 7,46</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,14; 15,06</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,7; 12,43</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,22; 11,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,04%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,5; 9,08</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,89; 8,19</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,73; 8,11</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.09323766261033282</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.049524342122901</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.07348760461594675</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5290</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2316</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7605</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.03895043629240849</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01413239480724707</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.03930276012162739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2210; 9666</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>661; 6147</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4067; 13239</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1703739229073569</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1314557211713337</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1279213414996147</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.05914297284000525</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.06078693220036759</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05992816801128286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>27875</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26195</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>54070</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.04117100006149257</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.04363135124942351</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.04808422830717492</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>19404; 37816</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>18802; 35861</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>43384; 67307</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.08023517092700917</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.08321648199338554</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.07460018642782679</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.09417837747412802</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.07865275354705054</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.08686520771408336</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>15861</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11796</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>27657</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.0613661679545533</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.0469994029611721</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.06223101845314732</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>10335; 25362</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7049; 18641</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19814; 38174</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1505877087814352</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1242910340141066</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1198943040111042</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.07039256836535702</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.06421683950011603</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.06746512981733177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>49026</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>40307</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>89332</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.05495578711370718</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.0488547151576424</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.05733751833272906</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>38275; 63224</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30664; 51401</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>75922; 107338</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.09077933455002261</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.08189150079235259</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.08106337165240766</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen otros (tasa de respuesta: 99,9%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2316</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>7605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2210</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>661</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>9666</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6147</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>13239</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>27875</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>26195</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>54070</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>19404</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>18802</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>43384</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>37816</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>35861</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>67307</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>15861</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>11796</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>27657</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>10335</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>7049</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>19814</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>25362</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>18641</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>38174</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>49026</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>40307</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>89332</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>38275</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>30664</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>75922</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>63224</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>51401</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>107338</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>